--- a/experiments/experiments_stigmergy_with_evaporation.xlsx
+++ b/experiments/experiments_stigmergy_with_evaporation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eashw\Desktop\post_graduation_plan\Collaborations\Swarm_collaboration_via_stigmergy\experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A249EA7C-2855-4752-BC98-8C42A6A23FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C14A69F-9B4C-421B-89C1-8A5C00794384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>grid_size</t>
   </si>
@@ -57,30 +57,6 @@
   </si>
   <si>
     <t>steps_to_complete</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1;0</t>
-  </si>
-  <si>
-    <t>9;12;4;10</t>
-  </si>
-  <si>
-    <t>4;17;19;9;12;3</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>38;77</t>
-  </si>
-  <si>
-    <t>19;21;52;91</t>
-  </si>
-  <si>
-    <t>26;43;52;77;97;179</t>
   </si>
   <si>
     <t>runs</t>
@@ -466,7 +442,7 @@
     <col min="4" max="4" width="9.68359375" customWidth="1"/>
     <col min="5" max="5" width="19.68359375" customWidth="1"/>
     <col min="6" max="6" width="18.68359375" customWidth="1"/>
-    <col min="7" max="7" width="20.68359375" customWidth="1"/>
+    <col min="7" max="7" width="12.68359375" customWidth="1"/>
     <col min="8" max="8" width="14.68359375" customWidth="1"/>
     <col min="9" max="9" width="11.68359375" customWidth="1"/>
     <col min="10" max="10" width="10.68359375" customWidth="1"/>
@@ -514,762 +490,642 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>80</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J2">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L2">
-        <v>1015</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>80</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J3">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L3">
-        <v>1304</v>
+        <v>897</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>80</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J4">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L4">
-        <v>713</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5">
-        <v>80</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J5">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L5">
-        <v>1359</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>80</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J6">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L6">
-        <v>2081</v>
+        <v>693</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J7">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L7">
-        <v>3425</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J8">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L8">
-        <v>2127</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J9">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L9">
-        <v>1546</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
       <c r="E10">
-        <v>100</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J10">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L10">
-        <v>2082</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="B11">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
         <v>10</v>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>5</v>
-      </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J11">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L11">
-        <v>2175</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>120</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J12">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L12">
-        <v>3614</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13">
-        <v>120</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J13">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L13">
-        <v>4405</v>
+        <v>4899</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>120</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J14">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L14">
-        <v>7597</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15">
-        <v>120</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J15">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L15">
-        <v>8532</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>120</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J16">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L16">
-        <v>5860</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>150</v>
-      </c>
-      <c r="F17" t="s">
         <v>15</v>
       </c>
-      <c r="G17" t="s">
-        <v>19</v>
-      </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J17">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L17">
-        <v>9119</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="B18">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>2</v>
       </c>
       <c r="E18">
-        <v>150</v>
-      </c>
-      <c r="F18" t="s">
         <v>15</v>
       </c>
-      <c r="G18" t="s">
-        <v>19</v>
-      </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J18">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L18">
-        <v>6551</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="B19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19">
-        <v>150</v>
-      </c>
-      <c r="F19" t="s">
         <v>15</v>
       </c>
-      <c r="G19" t="s">
-        <v>19</v>
-      </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J19">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L19">
-        <v>9203</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20">
-        <v>150</v>
-      </c>
-      <c r="F20" t="s">
         <v>15</v>
       </c>
-      <c r="G20" t="s">
-        <v>19</v>
-      </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J20">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L20">
-        <v>7509</v>
+        <v>4326</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>150</v>
-      </c>
-      <c r="F21" t="s">
         <v>15</v>
       </c>
-      <c r="G21" t="s">
-        <v>19</v>
-      </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J21">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="L21">
-        <v>7252</v>
+        <v>5413</v>
       </c>
     </row>
   </sheetData>
@@ -1279,23 +1135,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="11.68359375" customWidth="1"/>
     <col min="2" max="2" width="10.68359375" customWidth="1"/>
-    <col min="3" max="3" width="12.68359375" customWidth="1"/>
-    <col min="4" max="4" width="19.68359375" customWidth="1"/>
-    <col min="5" max="5" width="14.68359375" customWidth="1"/>
-    <col min="6" max="6" width="11.68359375" customWidth="1"/>
-    <col min="7" max="7" width="10.68359375" customWidth="1"/>
-    <col min="8" max="8" width="12.68359375" customWidth="1"/>
-    <col min="9" max="9" width="6.68359375" customWidth="1"/>
-    <col min="10" max="10" width="11.68359375" customWidth="1"/>
-    <col min="11" max="11" width="20.68359375" customWidth="1"/>
+    <col min="3" max="3" width="19.68359375" customWidth="1"/>
+    <col min="4" max="4" width="6.68359375" customWidth="1"/>
+    <col min="5" max="5" width="11.68359375" customWidth="1"/>
+    <col min="6" max="6" width="19.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1303,171 +1154,96 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>200</v>
+      </c>
+      <c r="B2">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>794.2</v>
+      </c>
+      <c r="F2">
+        <v>356.7642078460226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>300</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>2440</v>
+      </c>
+      <c r="F3">
+        <v>834.02787723193035</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>400</v>
+      </c>
+      <c r="B4">
         <v>20</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>3402.2</v>
+      </c>
+      <c r="F4">
+        <v>998.03542021313058</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>500</v>
+      </c>
+      <c r="B5">
         <v>25</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>80</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>60</v>
-      </c>
-      <c r="G2">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>1294.4000000000001</v>
-      </c>
-      <c r="K2">
-        <v>509.68009574634158</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>50</v>
-      </c>
-      <c r="B3">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>60</v>
-      </c>
-      <c r="G3">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
-        <v>2271</v>
-      </c>
-      <c r="K3">
-        <v>693.3639015697313</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>75</v>
-      </c>
-      <c r="B4">
+      <c r="C5">
         <v>15</v>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>120</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>60</v>
-      </c>
-      <c r="G4">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>6001.6</v>
-      </c>
-      <c r="K4">
-        <v>2074.7313802032299</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>100</v>
-      </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
       <c r="D5">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4234.3999999999996</v>
       </c>
       <c r="F5">
-        <v>60</v>
-      </c>
-      <c r="G5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>7926.8</v>
-      </c>
-      <c r="K5">
-        <v>1180.335206625643</v>
+        <v>773.70330230651086</v>
       </c>
     </row>
   </sheetData>
